--- a/docs/oc-mensuales/emergencias-contingencias-y-prevencion/ene-2026.xlsx
+++ b/docs/oc-mensuales/emergencias-contingencias-y-prevencion/ene-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>32934.53</v>
+        <v>32164.08</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>5202.55</v>
+        <v>5136.51</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>34460.99</v>
+        <v>34015.6</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>8615.25</v>
+        <v>8503.9</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>3054.73</v>
+        <v>3015.25</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>36529.38</v>
+        <v>36057.26</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>475.58</v>
+        <v>469.44</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>429.44</v>
+        <v>423.89</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>399.33</v>
+        <v>394.17</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>273.93</v>
+        <v>270.39</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>18229.04</v>
+        <v>17993.44</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>702.95</v>
+        <v>693.86</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>8615.25</v>
+        <v>8503.9</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>9054.290000000001</v>
+        <v>8937.27</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>420.53</v>
+        <v>415.09</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>401.17</v>
+        <v>395.98</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>8615.25</v>
+        <v>8503.9</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>401.17</v>
+        <v>395.98</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>2942.58</v>
+        <v>2904.55</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>36458.09</v>
+        <v>35986.89</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>8865.440000000001</v>
+        <v>8750.860000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>8615.25</v>
+        <v>8503.9</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>475.58</v>
+        <v>469.44</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>9058.42</v>
+        <v>8941.35</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>464.5</v>
+        <v>458.49</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>699.1</v>
+        <v>690.0700000000001</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>9058.42</v>
+        <v>8941.35</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>464.5</v>
+        <v>458.49</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>8615.25</v>
+        <v>8503.9</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>681.23</v>
+        <v>672.42</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>9846.58</v>
+        <v>9719.32</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>9577.02</v>
+        <v>9453.25</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>420.53</v>
+        <v>415.09</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>1521.12</v>
+        <v>1501.46</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>18116.68</v>
+        <v>17882.53</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>951.17</v>
+        <v>938.87</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>8615.25</v>
+        <v>8503.9</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>9114.52</v>
+        <v>8996.719999999999</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>467.23</v>
+        <v>461.19</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>9577.02</v>
+        <v>9453.25</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>475.58</v>
+        <v>469.44</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>9577.02</v>
+        <v>9453.25</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>9054.290000000001</v>
+        <v>8937.27</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>9114.52</v>
+        <v>8996.719999999999</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>67.58</v>
+        <v>66.70999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>17230.5</v>
+        <v>17007.8</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>67.58</v>
+        <v>66.70999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>9332.040000000001</v>
+        <v>9211.43</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>254.52</v>
+        <v>251.23</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>18229.04</v>
+        <v>17993.44</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>881.73</v>
+        <v>870.33</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>9058.42</v>
+        <v>8941.35</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>307.68</v>
+        <v>303.7</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>9058.42</v>
+        <v>8941.35</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>9921.129999999999</v>
+        <v>9792.91</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>568.6</v>
+        <v>561.25</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>475.58</v>
+        <v>469.44</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>518.66</v>
+        <v>511.96</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>9059.379999999999</v>
+        <v>8942.290000000001</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>807.28</v>
+        <v>796.84</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>518.66</v>
+        <v>511.96</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>9921.129999999999</v>
+        <v>9792.91</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>2013.39</v>
+        <v>2009.42</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>20521.57</v>
+        <v>20481.15</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>416.78</v>
+        <v>415.96</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>736.13</v>
+        <v>734.6799999999999</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>2123.49</v>
+        <v>2119.31</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>1601.88</v>
+        <v>1598.73</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>8627.07</v>
+        <v>8610.08</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>9059.379999999999</v>
+        <v>9041.540000000001</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>510.21</v>
+        <v>509.2</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>9847.879999999999</v>
+        <v>9828.49</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>672.83</v>
+        <v>671.5</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>936.42</v>
+        <v>936.4299999999999</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>475.58</v>
+        <v>475.59</v>
       </c>
     </row>
     <row r="77">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>10089.74</v>
+        <v>10089.8</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>405.45</v>
+        <v>405.46</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>8627.07</v>
+        <v>8627.120000000001</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>1129.09</v>
+        <v>1129.1</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>923.4400000000001</v>
+        <v>923.45</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>8627.07</v>
+        <v>8627.120000000001</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>475.58</v>
+        <v>475.59</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>9114.52</v>
+        <v>9114.58</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>9058.34</v>
+        <v>9058.4</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>3681.53</v>
+        <v>3686.64</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>1318.32</v>
+        <v>1320.15</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>1878.6</v>
+        <v>1881.2</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>1917.81</v>
+        <v>1916.5</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>2416.79</v>
+        <v>2415.14</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>7462.46</v>
+        <v>7457.36</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>27396.48</v>
+        <v>27377.77</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>9273.82</v>
+        <v>9267.49</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>9846.58</v>
+        <v>9839.85</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>6121.23</v>
+        <v>6117.05</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>9132.16</v>
+        <v>9125.92</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>9059.379999999999</v>
+        <v>9053.190000000001</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>510.21</v>
+        <v>509.86</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>495.54</v>
+        <v>495.2</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>554.63</v>
+        <v>554.25</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>635.55</v>
+        <v>635.11</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>3177.68</v>
+        <v>3175.51</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>8998.5</v>
+        <v>8992.360000000001</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>10645.8</v>
+        <v>10609.26</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>9808.450000000001</v>
+        <v>9774.780000000001</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>1393.49</v>
+        <v>1388.71</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>806.67</v>
+        <v>803.9</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>152.6</v>
+        <v>152.07</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>878.03</v>
+        <v>875.02</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>1039.08</v>
+        <v>1035.51</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>464.5</v>
+        <v>462.9</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>1931.81</v>
+        <v>1925.18</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>853.86</v>
+        <v>850.9299999999999</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>19646.1</v>
+        <v>19578.67</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>2344.96</v>
+        <v>2336.91</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>9921.129999999999</v>
+        <v>9887.08</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>487.99</v>
+        <v>486.31</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>994.85</v>
+        <v>991.4299999999999</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>63415.65</v>
+        <v>63198</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>5938.75</v>
+        <v>5918.37</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>5260.64</v>
+        <v>5242.58</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>42394.52</v>
+        <v>42249.02</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>2376.09</v>
+        <v>2367.94</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>5346.09</v>
+        <v>5327.75</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>12290.12</v>
+        <v>12247.94</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>20911.94</v>
+        <v>20840.17</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>554.6</v>
+        <v>552.6900000000001</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>2731.92</v>
+        <v>2722.55</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>3713.19</v>
+        <v>3700.44</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>4709.35</v>
+        <v>4684.48</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>483.76</v>
+        <v>481.2</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>548.8099999999999</v>
+        <v>545.91</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>734.88</v>
+        <v>731</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>637.9400000000001</v>
+        <v>634.5700000000001</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>4658.95</v>
+        <v>4634.34</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>9808.450000000001</v>
+        <v>9756.639999999999</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>1023.12</v>
+        <v>1017.71</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>1033.44</v>
+        <v>1027.98</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>380.82</v>
+        <v>378.81</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>23605.99</v>
+        <v>23481.3</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>697.42</v>
+        <v>693.73</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>20613.11</v>
+        <v>20504.22</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>18846.89</v>
+        <v>18747.33</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>11727.97</v>
+        <v>11666.02</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>578.58</v>
+        <v>575.52</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>14941.86</v>
+        <v>14862.93</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>80908.91</v>
+        <v>80481.50999999999</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>73336.06</v>
+        <v>72948.66</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>8441.84</v>
+        <v>8397.25</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>43092.06</v>
+        <v>42864.43</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>17368.21</v>
+        <v>17276.47</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>22949.79</v>
+        <v>22828.56</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>58178.92</v>
+        <v>57871.59</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>9690.24</v>
+        <v>9639.049999999999</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>635.55</v>
+        <v>632.1900000000001</v>
       </c>
     </row>
     <row r="158">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>14163.37</v>
+        <v>14088.55</v>
       </c>
     </row>
     <row r="159">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>21924.41</v>
+        <v>21787.02</v>
       </c>
     </row>
     <row r="160">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>110849.84</v>
+        <v>110155.2</v>
       </c>
     </row>
     <row r="161">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>309.16</v>
+        <v>307.23</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>1778.47</v>
+        <v>1767.33</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>727.38</v>
+        <v>722.83</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>695.8200000000001</v>
+        <v>691.46</v>
       </c>
     </row>
     <row r="165">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>3532.01</v>
+        <v>3509.88</v>
       </c>
     </row>
     <row r="166">
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>18049.32</v>
+        <v>17936.21</v>
       </c>
     </row>
     <row r="167">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>1154.97</v>
+        <v>1147.73</v>
       </c>
     </row>
     <row r="168">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>5750.99</v>
+        <v>5714.95</v>
       </c>
     </row>
     <row r="169">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>10090.13</v>
+        <v>10026.9</v>
       </c>
     </row>
     <row r="170">
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>8658.82</v>
+        <v>8604.559999999999</v>
       </c>
     </row>
     <row r="171">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>8615.25</v>
+        <v>8561.26</v>
       </c>
     </row>
     <row r="172">
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>409.28</v>
+        <v>406.72</v>
       </c>
     </row>
     <row r="173">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>6373.75</v>
+        <v>6333.81</v>
       </c>
     </row>
     <row r="174">
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>25883.94</v>
+        <v>25721.74</v>
       </c>
     </row>
     <row r="175">
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>8615.25</v>
+        <v>8561.26</v>
       </c>
     </row>
     <row r="176">
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>1960.55</v>
+        <v>1948.26</v>
       </c>
     </row>
     <row r="177">
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>10204.24</v>
+        <v>10140.3</v>
       </c>
     </row>
     <row r="178">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>113753.07</v>
+        <v>113040.23</v>
       </c>
     </row>
     <row r="179">
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>2988.31</v>
+        <v>2969.58</v>
       </c>
     </row>
     <row r="180">
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>133425.18</v>
+        <v>132589.07</v>
       </c>
     </row>
     <row r="181">
@@ -11488,7 +11488,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>507.87</v>
+        <v>504.69</v>
       </c>
     </row>
     <row r="182">
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>66793.36</v>
+        <v>66374.8</v>
       </c>
     </row>
     <row r="183">
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>133422.48</v>
+        <v>132586.39</v>
       </c>
     </row>
     <row r="184">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>578.58</v>
+        <v>574.95</v>
       </c>
     </row>
     <row r="185">
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>10645.8</v>
+        <v>10715.57</v>
       </c>
     </row>
     <row r="186">
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>2542.19</v>
+        <v>2558.85</v>
       </c>
     </row>
     <row r="187">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>814.6</v>
+        <v>819.9400000000001</v>
       </c>
     </row>
     <row r="188">
@@ -11915,7 +11915,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>2577.53</v>
+        <v>2594.42</v>
       </c>
     </row>
     <row r="189">
@@ -11976,7 +11976,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>6717.16</v>
+        <v>6761.19</v>
       </c>
     </row>
     <row r="190">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>38263.19</v>
+        <v>38513.96</v>
       </c>
     </row>
     <row r="191">
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>16962.2</v>
+        <v>17073.37</v>
       </c>
     </row>
     <row r="192">
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>493.01</v>
+        <v>496.24</v>
       </c>
     </row>
     <row r="193">
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>24586.03</v>
+        <v>24747.17</v>
       </c>
     </row>
     <row r="194">
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>35689.25</v>
+        <v>35923.15</v>
       </c>
     </row>
     <row r="195">
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>26972.59</v>
+        <v>27149.36</v>
       </c>
     </row>
     <row r="196">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>578.58</v>
+        <v>582.37</v>
       </c>
     </row>
     <row r="197">
@@ -12464,7 +12464,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>65019.06</v>
+        <v>65445.19</v>
       </c>
     </row>
     <row r="198">
@@ -12525,7 +12525,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>59792.48</v>
+        <v>60184.35</v>
       </c>
     </row>
     <row r="199">
@@ -12586,7 +12586,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>172.81</v>
+        <v>173.94</v>
       </c>
     </row>
     <row r="200">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>74331.58</v>
+        <v>74818.74000000001</v>
       </c>
     </row>
     <row r="201">
@@ -12708,7 +12708,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>33396.68</v>
+        <v>33615.56</v>
       </c>
     </row>
     <row r="202">
@@ -12769,7 +12769,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>2669.32</v>
+        <v>2686.82</v>
       </c>
     </row>
     <row r="203">
@@ -12830,7 +12830,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>7754.15</v>
+        <v>7804.97</v>
       </c>
     </row>
     <row r="204">
@@ -12891,7 +12891,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>1480.83</v>
+        <v>1490.53</v>
       </c>
     </row>
     <row r="205">
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>10938.6</v>
+        <v>11010.29</v>
       </c>
     </row>
     <row r="206">
@@ -13013,7 +13013,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>5355.21</v>
+        <v>5390.31</v>
       </c>
     </row>
     <row r="207">
@@ -13074,7 +13074,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>2358.41</v>
+        <v>2390.17</v>
       </c>
     </row>
     <row r="208">
@@ -13135,7 +13135,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>2180.85</v>
+        <v>2210.22</v>
       </c>
     </row>
     <row r="209">
@@ -13196,7 +13196,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>3775.31</v>
+        <v>3826.15</v>
       </c>
     </row>
     <row r="210">
@@ -13257,7 +13257,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>29469.15</v>
+        <v>29866</v>
       </c>
     </row>
     <row r="211">
@@ -13318,7 +13318,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>3151.34</v>
+        <v>3193.77</v>
       </c>
     </row>
     <row r="212">
@@ -13379,7 +13379,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>18264.32</v>
+        <v>18510.28</v>
       </c>
     </row>
     <row r="213">
@@ -13440,7 +13440,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>699.49</v>
+        <v>708.91</v>
       </c>
     </row>
     <row r="214">
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>294117.69</v>
+        <v>298078.41</v>
       </c>
     </row>
     <row r="215">
@@ -13562,7 +13562,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>6157.54</v>
+        <v>6240.46</v>
       </c>
     </row>
     <row r="216">
@@ -13623,7 +13623,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>9058.34</v>
+        <v>9180.32</v>
       </c>
     </row>
     <row r="217">
@@ -13684,7 +13684,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>135890.68</v>
+        <v>137720.64</v>
       </c>
     </row>
     <row r="218">
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>7822.87</v>
+        <v>7928.22</v>
       </c>
     </row>
     <row r="219">
@@ -13806,7 +13806,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>3424.75</v>
+        <v>3470.87</v>
       </c>
     </row>
     <row r="220">
@@ -13867,7 +13867,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>7483.96</v>
+        <v>7584.75</v>
       </c>
     </row>
     <row r="221">
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>139790.04</v>
+        <v>141672.51</v>
       </c>
     </row>
     <row r="222">
@@ -13989,7 +13989,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>7079.87</v>
+        <v>7175.21</v>
       </c>
     </row>
     <row r="223">
@@ -14050,7 +14050,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>17083.57</v>
+        <v>17313.62</v>
       </c>
     </row>
     <row r="224">
@@ -14111,7 +14111,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>17083.57</v>
+        <v>17313.62</v>
       </c>
     </row>
     <row r="225">
@@ -14172,7 +14172,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>51250.7</v>
+        <v>51940.86</v>
       </c>
     </row>
     <row r="226">
@@ -14233,7 +14233,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>7056.51</v>
+        <v>7151.54</v>
       </c>
     </row>
     <row r="227">
@@ -14294,7 +14294,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>60395.87</v>
+        <v>61209.19</v>
       </c>
     </row>
     <row r="228">
@@ -14355,7 +14355,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>430348.43</v>
+        <v>436143.69</v>
       </c>
     </row>
     <row r="229">
@@ -14416,7 +14416,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>10234.94</v>
+        <v>10372.77</v>
       </c>
     </row>
     <row r="230">
@@ -14477,7 +14477,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>4470.76</v>
+        <v>4530.96</v>
       </c>
     </row>
     <row r="231">
@@ -14538,7 +14538,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>430.25</v>
+        <v>436.04</v>
       </c>
     </row>
     <row r="232">
@@ -14599,7 +14599,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>51767.89</v>
+        <v>52465.02</v>
       </c>
     </row>
     <row r="233">
@@ -14660,7 +14660,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>983.42</v>
+        <v>996.66</v>
       </c>
     </row>
     <row r="234">
@@ -14721,7 +14721,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>1020.42</v>
+        <v>1034.16</v>
       </c>
     </row>
     <row r="235">
@@ -14782,7 +14782,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>1050639.26</v>
+        <v>1064787.63</v>
       </c>
     </row>
     <row r="236">
@@ -14843,7 +14843,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>103535.78</v>
+        <v>104930.04</v>
       </c>
     </row>
     <row r="237">
@@ -14904,7 +14904,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>18118.76</v>
+        <v>18362.75</v>
       </c>
     </row>
     <row r="238">
@@ -14965,7 +14965,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>4815.05</v>
+        <v>4888.36</v>
       </c>
     </row>
     <row r="239">
@@ -15026,7 +15026,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>9921.129999999999</v>
+        <v>10072.17</v>
       </c>
     </row>
     <row r="240">
@@ -15087,7 +15087,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>741.11</v>
+        <v>752.39</v>
       </c>
     </row>
     <row r="241">
@@ -15148,7 +15148,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>67718.2</v>
+        <v>68749.14999999999</v>
       </c>
     </row>
     <row r="242">
@@ -15209,7 +15209,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>2826.16</v>
+        <v>2869.19</v>
       </c>
     </row>
     <row r="243">
@@ -15270,7 +15270,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>292297.01</v>
+        <v>296746.95</v>
       </c>
     </row>
     <row r="244">
@@ -15331,7 +15331,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>66711.24000000001</v>
+        <v>67726.86</v>
       </c>
     </row>
     <row r="245">
@@ -15392,7 +15392,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>102527.59</v>
+        <v>104088.47</v>
       </c>
     </row>
     <row r="246">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>55378.88</v>
+        <v>56221.97</v>
       </c>
     </row>
     <row r="247">
@@ -15514,7 +15514,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>185828.94</v>
+        <v>188658</v>
       </c>
     </row>
     <row r="248">
@@ -15575,7 +15575,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>198704.06</v>
+        <v>201729.13</v>
       </c>
     </row>
     <row r="249">
@@ -15636,7 +15636,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>237923.75</v>
+        <v>241545.91</v>
       </c>
     </row>
     <row r="250">
@@ -15697,7 +15697,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>32555.3</v>
+        <v>33050.92</v>
       </c>
     </row>
     <row r="251">
@@ -15758,7 +15758,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>62276.84</v>
+        <v>63224.94</v>
       </c>
     </row>
     <row r="252">
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>978.4400000000001</v>
+        <v>993.33</v>
       </c>
     </row>
     <row r="253">
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>123850.69</v>
+        <v>125736.19</v>
       </c>
     </row>
     <row r="254">
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>458.52</v>
+        <v>465.5</v>
       </c>
     </row>
     <row r="255">
@@ -16002,7 +16002,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>27178.14</v>
+        <v>27591.9</v>
       </c>
     </row>
     <row r="256">
@@ -16063,7 +16063,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>322.46</v>
+        <v>327.37</v>
       </c>
     </row>
     <row r="257">
@@ -16124,7 +16124,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>676.92</v>
+        <v>687.22</v>
       </c>
     </row>
     <row r="258">
@@ -16185,7 +16185,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>441.21</v>
+        <v>447.92</v>
       </c>
     </row>
     <row r="259">
@@ -16246,7 +16246,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>2539.37</v>
+        <v>2578.03</v>
       </c>
     </row>
     <row r="260">
@@ -16307,7 +16307,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>25625.35</v>
+        <v>26015.47</v>
       </c>
     </row>
     <row r="261">
@@ -16368,7 +16368,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>14466.28</v>
+        <v>14686.51</v>
       </c>
     </row>
     <row r="262">
@@ -16429,7 +16429,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>8773.780000000001</v>
+        <v>8907.35</v>
       </c>
     </row>
     <row r="263">
@@ -16490,7 +16490,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>8541.780000000001</v>
+        <v>8671.82</v>
       </c>
     </row>
     <row r="264">
@@ -16551,7 +16551,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>3706.08</v>
+        <v>3762.5</v>
       </c>
     </row>
     <row r="265">
@@ -16612,7 +16612,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>47885.12</v>
+        <v>48614.12</v>
       </c>
     </row>
     <row r="266">
@@ -16673,7 +16673,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>817.47</v>
+        <v>829.91</v>
       </c>
     </row>
     <row r="267">
@@ -16734,7 +16734,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>454.19</v>
+        <v>461.11</v>
       </c>
     </row>
     <row r="268">
@@ -16795,7 +16795,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>219.76</v>
+        <v>223.11</v>
       </c>
     </row>
     <row r="269">
@@ -16856,7 +16856,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>9470.58</v>
+        <v>9614.76</v>
       </c>
     </row>
     <row r="270">
@@ -16917,7 +16917,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>554.51</v>
+        <v>562.95</v>
       </c>
     </row>
     <row r="271">
@@ -16978,7 +16978,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>705.7</v>
+        <v>716.45</v>
       </c>
     </row>
     <row r="272">
@@ -17039,7 +17039,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>162293.87</v>
+        <v>164764.63</v>
       </c>
     </row>
     <row r="273">
@@ -17100,7 +17100,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>62729.43</v>
+        <v>64254.87</v>
       </c>
     </row>
     <row r="274">
@@ -17161,7 +17161,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>93959.61</v>
+        <v>96244.49000000001</v>
       </c>
     </row>
     <row r="275">
@@ -17222,7 +17222,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>7532.76</v>
+        <v>7715.93</v>
       </c>
     </row>
     <row r="276">
@@ -17283,7 +17283,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>45917.02</v>
+        <v>47033.61</v>
       </c>
     </row>
     <row r="277">
@@ -17344,7 +17344,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>112158.74</v>
+        <v>114886.19</v>
       </c>
     </row>
     <row r="278">
@@ -17405,7 +17405,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>4173.66</v>
+        <v>4275.15</v>
       </c>
     </row>
     <row r="279">
@@ -17466,7 +17466,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>11846.22</v>
+        <v>12134.29</v>
       </c>
     </row>
     <row r="280">
@@ -17527,7 +17527,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>9823.049999999999</v>
+        <v>10061.92</v>
       </c>
     </row>
     <row r="281">
@@ -17588,7 +17588,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>3413.71</v>
+        <v>3496.72</v>
       </c>
     </row>
     <row r="282">
@@ -17649,7 +17649,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>9577.02</v>
+        <v>9809.91</v>
       </c>
     </row>
     <row r="283">
@@ -17710,7 +17710,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>13311.96</v>
+        <v>13635.68</v>
       </c>
     </row>
     <row r="284">
@@ -17771,7 +17771,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>1529.99</v>
+        <v>1567.19</v>
       </c>
     </row>
     <row r="285">
@@ -17832,7 +17832,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>9823.049999999999</v>
+        <v>10061.92</v>
       </c>
     </row>
     <row r="286">
@@ -17893,7 +17893,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>9921.129999999999</v>
+        <v>10162.39</v>
       </c>
     </row>
     <row r="287">
@@ -17954,7 +17954,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>2625.53</v>
+        <v>2689.38</v>
       </c>
     </row>
     <row r="288">
@@ -18015,7 +18015,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>1271.1</v>
+        <v>1302.01</v>
       </c>
     </row>
     <row r="289">
@@ -18076,7 +18076,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>19815.07</v>
+        <v>20296.93</v>
       </c>
     </row>
     <row r="290">
@@ -18137,7 +18137,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>5084.29</v>
+        <v>5207.92</v>
       </c>
     </row>
     <row r="291">
@@ -18198,7 +18198,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>5598.67</v>
+        <v>5734.82</v>
       </c>
     </row>
     <row r="292">
@@ -18259,7 +18259,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>9070.74</v>
+        <v>9291.32</v>
       </c>
     </row>
     <row r="293">
@@ -18320,7 +18320,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>2381.65</v>
+        <v>2439.56</v>
       </c>
     </row>
     <row r="294">
@@ -18381,7 +18381,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>3008.27</v>
+        <v>3081.42</v>
       </c>
     </row>
     <row r="295">
@@ -18442,7 +18442,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>49893.09</v>
+        <v>51154.39</v>
       </c>
     </row>
     <row r="296">
@@ -18503,7 +18503,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>6267.02</v>
+        <v>6425.45</v>
       </c>
     </row>
     <row r="297">
@@ -18564,7 +18564,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>128126.74</v>
+        <v>131365.79</v>
       </c>
     </row>
     <row r="298">
@@ -18625,7 +18625,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>20613.11</v>
+        <v>21134.21</v>
       </c>
     </row>
     <row r="299">
@@ -18686,7 +18686,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>68334.25999999999</v>
+        <v>70061.75</v>
       </c>
     </row>
     <row r="300">
@@ -18747,7 +18747,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>21505.34</v>
+        <v>22049</v>
       </c>
     </row>
     <row r="301">
@@ -18808,7 +18808,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>1329.43</v>
+        <v>1363.04</v>
       </c>
     </row>
     <row r="302">
@@ -18869,7 +18869,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>1516.04</v>
+        <v>1554.36</v>
       </c>
     </row>
     <row r="303">
@@ -18930,7 +18930,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>9907.540000000001</v>
+        <v>10158</v>
       </c>
     </row>
     <row r="304">
@@ -18991,7 +18991,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>10595.9</v>
+        <v>10863.77</v>
       </c>
     </row>
     <row r="305">
@@ -19052,7 +19052,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>59792.48</v>
+        <v>61304.03</v>
       </c>
     </row>
     <row r="306">
@@ -19113,7 +19113,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>929.49</v>
+        <v>952.98</v>
       </c>
     </row>
     <row r="307">
@@ -19174,7 +19174,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>69023.85000000001</v>
+        <v>70768.78</v>
       </c>
     </row>
     <row r="308">
@@ -19235,7 +19235,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>7340.18</v>
+        <v>7525.74</v>
       </c>
     </row>
     <row r="309">
@@ -19296,7 +19296,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>5153.3</v>
+        <v>5283.57</v>
       </c>
     </row>
     <row r="310">
@@ -19357,7 +19357,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>21291.6</v>
+        <v>21829.85</v>
       </c>
     </row>
     <row r="311">
@@ -19418,7 +19418,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>6247.22</v>
+        <v>6405.15</v>
       </c>
     </row>
     <row r="312">
@@ -19479,7 +19479,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>641.48</v>
+        <v>657.7</v>
       </c>
     </row>
     <row r="313">
@@ -19540,7 +19540,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>510.21</v>
+        <v>525.6799999999999</v>
       </c>
     </row>
     <row r="314">
@@ -19601,7 +19601,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>3481.18</v>
+        <v>3586.74</v>
       </c>
     </row>
     <row r="315">
@@ -19662,7 +19662,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>213544.56</v>
+        <v>220019.9</v>
       </c>
     </row>
     <row r="316">
@@ -19723,7 +19723,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>24074.71</v>
+        <v>24804.73</v>
       </c>
     </row>
     <row r="317">
@@ -19784,7 +19784,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>3562.06</v>
+        <v>3670.07</v>
       </c>
     </row>
     <row r="318">
@@ -19845,7 +19845,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>9808.450000000001</v>
+        <v>10105.87</v>
       </c>
     </row>
     <row r="319">
@@ -19906,7 +19906,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>9054.290000000001</v>
+        <v>9328.84</v>
       </c>
     </row>
     <row r="320">
@@ -19967,7 +19967,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>26924.11</v>
+        <v>27740.53</v>
       </c>
     </row>
     <row r="321">
@@ -20028,7 +20028,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>813.01</v>
+        <v>837.66</v>
       </c>
     </row>
     <row r="322">
@@ -20089,7 +20089,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>9059.379999999999</v>
+        <v>9334.09</v>
       </c>
     </row>
     <row r="323">
@@ -20150,7 +20150,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>475.79</v>
+        <v>490.22</v>
       </c>
     </row>
     <row r="324">
@@ -20211,7 +20211,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>272.44</v>
+        <v>280.7</v>
       </c>
     </row>
     <row r="325">
@@ -20272,7 +20272,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>553.59</v>
+        <v>570.37</v>
       </c>
     </row>
     <row r="326">
@@ -20333,7 +20333,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>140.57</v>
+        <v>144.83</v>
       </c>
     </row>
     <row r="327">
@@ -20394,7 +20394,7 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>9577.02</v>
+        <v>9867.43</v>
       </c>
     </row>
     <row r="328">
@@ -20455,7 +20455,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>32308.95</v>
+        <v>33288.65</v>
       </c>
     </row>
     <row r="329">
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>7185.98</v>
+        <v>7403.88</v>
       </c>
     </row>
     <row r="330">
@@ -20577,7 +20577,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>635.12</v>
+        <v>654.38</v>
       </c>
     </row>
     <row r="331">
@@ -20638,7 +20638,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>939.02</v>
+        <v>967.49</v>
       </c>
     </row>
     <row r="332">
@@ -20699,7 +20699,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>645.51</v>
+        <v>665.09</v>
       </c>
     </row>
     <row r="333">
@@ -20760,7 +20760,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>13812.07</v>
+        <v>14222.61</v>
       </c>
     </row>
     <row r="334">
@@ -20821,7 +20821,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>111043.17</v>
+        <v>114343.71</v>
       </c>
     </row>
     <row r="335">
@@ -20882,7 +20882,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>72434.3</v>
+        <v>74587.25999999999</v>
       </c>
     </row>
     <row r="336">
@@ -20943,7 +20943,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>19646.1</v>
+        <v>20230.04</v>
       </c>
     </row>
     <row r="337">
@@ -21004,7 +21004,7 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>2699.9</v>
+        <v>2780.15</v>
       </c>
     </row>
     <row r="338">
@@ -21065,7 +21065,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>9833.77</v>
+        <v>10126.06</v>
       </c>
     </row>
     <row r="339">
@@ -21126,7 +21126,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>1138.48</v>
+        <v>1172.32</v>
       </c>
     </row>
     <row r="340">
@@ -21187,7 +21187,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>7396.24</v>
+        <v>7616.08</v>
       </c>
     </row>
     <row r="341">
@@ -21248,7 +21248,7 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>21065.31</v>
+        <v>21691.44</v>
       </c>
     </row>
     <row r="342">
@@ -21309,7 +21309,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>9907.540000000001</v>
+        <v>10202.02</v>
       </c>
     </row>
     <row r="343">
@@ -21370,7 +21370,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>9059.379999999999</v>
+        <v>9328.65</v>
       </c>
     </row>
     <row r="344">
@@ -21431,7 +21431,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>94907.8</v>
+        <v>97728.74000000001</v>
       </c>
     </row>
     <row r="345">
@@ -21492,7 +21492,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>3204.83</v>
+        <v>3300.09</v>
       </c>
     </row>
     <row r="346">
@@ -21553,7 +21553,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>51767.89</v>
+        <v>53306.59</v>
       </c>
     </row>
     <row r="347">
@@ -21614,7 +21614,7 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>7118.73</v>
+        <v>7330.32</v>
       </c>
     </row>
     <row r="348">
@@ -21675,7 +21675,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>172128.19</v>
+        <v>177244.36</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/emergencias-contingencias-y-prevencion/ene-2026.xlsx
+++ b/docs/oc-mensuales/emergencias-contingencias-y-prevencion/ene-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC ene-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC ene-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -18117,7 +18117,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -18300,7 +18300,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">

--- a/docs/oc-mensuales/emergencias-contingencias-y-prevencion/ene-2026.xlsx
+++ b/docs/oc-mensuales/emergencias-contingencias-y-prevencion/ene-2026.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Escuela de Gendarmería</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (V)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (V)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6217,7 +6217,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6339,7 +6339,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6644,7 +6644,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7132,7 +7132,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7437,7 +7437,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7732,7 +7732,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7925,7 +7925,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8047,7 +8047,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8108,7 +8108,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8169,7 +8169,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8230,7 +8230,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8352,7 +8352,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8657,7 +8657,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8779,7 +8779,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA CARAB ARAUCANÍA CONT ORD PUBL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -9023,7 +9023,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9084,7 +9084,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9145,7 +9145,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9328,7 +9328,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9389,7 +9389,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9562,7 +9562,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -9572,7 +9572,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9694,7 +9694,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9755,7 +9755,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9938,7 +9938,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -9999,7 +9999,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10060,7 +10060,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10182,7 +10182,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10243,7 +10243,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10365,7 +10365,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10426,7 +10426,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10548,7 +10548,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10680,7 +10680,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA expressVirtual SpA</t>
+          <t>COMERCIALIZADORA EXPRESSVIRTUAL SPA</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -10731,7 +10731,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -10853,7 +10853,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -10975,7 +10975,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11036,7 +11036,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11097,7 +11097,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11158,7 +11158,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11280,7 +11280,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11402,7 +11402,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -11524,7 +11524,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -11585,7 +11585,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -11646,7 +11646,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -11707,7 +11707,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -11768,7 +11768,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -11829,7 +11829,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -12134,7 +12134,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12195,7 +12195,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12256,7 +12256,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -12317,7 +12317,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -12378,7 +12378,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -12439,7 +12439,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -12500,7 +12500,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -12561,7 +12561,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -12622,7 +12622,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -12683,7 +12683,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -12988,7 +12988,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13049,7 +13049,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13171,7 +13171,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13232,7 +13232,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13293,7 +13293,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -13354,7 +13354,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -13415,7 +13415,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -13476,7 +13476,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -13598,7 +13598,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -13659,7 +13659,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -13669,7 +13669,7 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
@@ -13781,7 +13781,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -13842,7 +13842,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -13903,7 +13903,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -13964,7 +13964,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -14025,7 +14025,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -14086,7 +14086,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -14147,7 +14147,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -14208,7 +14208,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -14269,7 +14269,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -14330,7 +14330,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -14340,7 +14340,7 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>Heraldo Castro Palma</t>
+          <t>HERALDO CASTRO PALMA</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
@@ -14391,7 +14391,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -14452,7 +14452,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -14513,7 +14513,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -14635,7 +14635,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -14696,7 +14696,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -14818,7 +14818,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -14879,7 +14879,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -14889,7 +14889,7 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
@@ -14940,7 +14940,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -15001,7 +15001,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -15062,7 +15062,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -15123,7 +15123,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -15184,7 +15184,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -15245,7 +15245,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -15255,7 +15255,7 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>SUPERMERCADO MAYORISTA METROPOLITANO</t>
+          <t>supermercado mayorista metropolitano</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -15306,7 +15306,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -15367,7 +15367,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -15428,7 +15428,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -15489,7 +15489,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -15550,7 +15550,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -15611,7 +15611,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -15672,7 +15672,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -15733,7 +15733,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -15794,7 +15794,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -15916,7 +15916,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -15977,7 +15977,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -15987,7 +15987,7 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
@@ -16038,7 +16038,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -16099,7 +16099,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -16221,7 +16221,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -16282,7 +16282,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -16343,7 +16343,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -16404,7 +16404,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -16465,7 +16465,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -16526,7 +16526,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -16587,7 +16587,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -16648,7 +16648,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -16709,7 +16709,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -16770,7 +16770,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -16831,7 +16831,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -16841,7 +16841,7 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
@@ -16892,7 +16892,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -16953,7 +16953,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -17014,7 +17014,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -17075,7 +17075,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -17136,7 +17136,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -17197,7 +17197,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -17258,7 +17258,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -17319,7 +17319,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -17380,7 +17380,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -17441,7 +17441,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -17502,7 +17502,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -17624,7 +17624,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -17746,7 +17746,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -17807,7 +17807,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -17868,7 +17868,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -17929,7 +17929,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -17990,7 +17990,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -18051,7 +18051,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -18173,7 +18173,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE VITACURA</t>
+          <t>I MUNICIPALIDAD DE VITACURA</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -18356,7 +18356,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -18417,7 +18417,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -18478,7 +18478,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -18539,7 +18539,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -18661,7 +18661,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -18722,7 +18722,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -18905,7 +18905,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -18966,7 +18966,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -19027,7 +19027,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -19088,7 +19088,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -19149,7 +19149,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -19210,7 +19210,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -19332,7 +19332,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -19393,7 +19393,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -19454,7 +19454,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -19515,7 +19515,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -19576,7 +19576,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -19637,7 +19637,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -19698,7 +19698,7 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -19759,7 +19759,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -19820,7 +19820,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -19881,7 +19881,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -19891,7 +19891,7 @@
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J319" t="inlineStr">
@@ -20003,7 +20003,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -20064,7 +20064,7 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -20074,7 +20074,7 @@
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J322" t="inlineStr">
@@ -20125,7 +20125,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -20186,7 +20186,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -20247,7 +20247,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -20308,7 +20308,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -20369,7 +20369,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -20435,7 +20435,7 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -20491,7 +20491,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -20552,7 +20552,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -20613,7 +20613,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -20674,7 +20674,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -20796,7 +20796,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -20857,7 +20857,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -20867,7 +20867,7 @@
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
@@ -20918,7 +20918,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -20979,7 +20979,7 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -21040,7 +21040,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -21101,7 +21101,7 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -21162,7 +21162,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -21223,7 +21223,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -21284,7 +21284,7 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -21345,7 +21345,7 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -21355,7 +21355,7 @@
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J343" t="inlineStr">
@@ -21406,7 +21406,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -21467,7 +21467,7 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
@@ -21528,7 +21528,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
@@ -21589,7 +21589,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -21650,7 +21650,7 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -21660,7 +21660,7 @@
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J348" t="inlineStr">

--- a/docs/oc-mensuales/emergencias-contingencias-y-prevencion/ene-2026.xlsx
+++ b/docs/oc-mensuales/emergencias-contingencias-y-prevencion/ene-2026.xlsx
@@ -562,7 +562,11 @@
           <t>77.721.492-6</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +932,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +997,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1062,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1127,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1253,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1440,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1505,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1631,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1940,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2127,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2375,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2562,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2749,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +2936,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3062,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3310,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3436,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3684,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +3993,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4058,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4123,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4188,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4253,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4318,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4505,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4570,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4696,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4761,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +4887,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +4952,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5078,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5143,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5208,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5273,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5460,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5647,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5773,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +5960,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6147,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6212,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6643,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6708,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +6895,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +6960,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7208,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7273,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7460,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7525,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +7773,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +7899,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8086,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8273,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8399,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8586,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +8834,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8736,7 +8960,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9025,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9151,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9216,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9281,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9346,11 @@
           <t>77.544.929-2</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9533,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +9903,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +9968,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +10033,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10098,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10017,7 +10285,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10078,7 +10350,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10476,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10541,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10383,7 +10667,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10932,7 +11220,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10993,7 +11285,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11176,7 +11472,11 @@
           <t>76.102.347-0</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11237,7 +11537,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +11602,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11359,7 +11667,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +11732,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11786,7 +12102,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11847,7 +12167,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11969,7 +12293,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12030,7 +12358,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12091,7 +12423,11 @@
           <t>77.544.929-2</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12213,7 +12549,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12335,7 +12675,11 @@
           <t>78.616.370-6</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12457,7 +12801,11 @@
           <t>78.616.370-6</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +12927,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12640,7 +12992,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12762,7 +13118,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12884,7 +13244,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12945,7 +13309,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13189,7 +13557,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13738,7 +14110,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13799,7 +14175,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14409,7 +14789,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14470,7 +14854,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14714,7 +15102,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14958,7 +15350,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15080,7 +15476,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15385,7 +15785,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15507,7 +15911,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15751,7 +16159,11 @@
           <t>77.544.929-2</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16239,7 +16651,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16422,7 +16838,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16544,7 +16964,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16666,7 +17090,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16788,7 +17216,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17581,7 +18013,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17703,7 +18139,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18008,7 +18448,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18130,7 +18574,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18252,7 +18700,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18313,7 +18765,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19228,7 +19684,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19289,7 +19749,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19960,7 +20424,11 @@
           <t>78.094.280-0</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20204,7 +20672,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20448,7 +20920,11 @@
           <t>77.798.686-4</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20753,7 +21229,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21180,7 +21660,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21485,7 +21969,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21607,7 +22095,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
